--- a/assets/gravity-spaceship/level-design/关卡细节.xlsx
+++ b/assets/gravity-spaceship/level-design/关卡细节.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AF6E3D-074F-4784-B2E8-DC5DAA91250F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="851" firstSheet="47" activeTab="68" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="851" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
